--- a/contenido/classificacio.xlsx
+++ b/contenido/classificacio.xlsx
@@ -14658,7 +14658,11 @@
           <t>Pagina del web actual</t>
         </is>
       </c>
-      <c r="L242" s="2" t="inlineStr"/>
+      <c r="L242" s="2" t="inlineStr">
+        <is>
+          <t>Valua Services = aquesta pàgina (Gonçal, 07/10/2026).</t>
+        </is>
+      </c>
       <c r="M242" t="inlineStr">
         <is>
           <t>Públic</t>
@@ -17142,12 +17146,12 @@
       </c>
       <c r="L284" s="2" t="inlineStr">
         <is>
-          <t>Gonçal ha de confirmar si es publica. Preus del XML de 2018–2019: no fiables.</t>
+          <t>Gonçal ha de confirmar si es publica. Preus del XML de 2018–2019: no fiables. | STANDBY (Gonçal, 07/10/2026): no es publica ni es porta a la web nova per ara.</t>
         </is>
       </c>
       <c r="M284" s="2" t="inlineStr">
         <is>
-          <t>Esborrany</t>
+          <t>Standby</t>
         </is>
       </c>
       <c r="N284" s="2" t="inlineStr">
@@ -17198,12 +17202,12 @@
       </c>
       <c r="L285" s="2" t="inlineStr">
         <is>
-          <t>Gonçal ha de confirmar si es publica. Preus del XML de 2018–2019: no fiables.</t>
+          <t>Gonçal ha de confirmar si es publica. Preus del XML de 2018–2019: no fiables. | STANDBY (Gonçal, 07/10/2026): no es publica ni es porta a la web nova per ara.</t>
         </is>
       </c>
       <c r="M285" s="2" t="inlineStr">
         <is>
-          <t>Esborrany</t>
+          <t>Standby</t>
         </is>
       </c>
       <c r="N285" s="2" t="inlineStr">
@@ -17254,12 +17258,12 @@
       </c>
       <c r="L286" s="2" t="inlineStr">
         <is>
-          <t>Gonçal ha de confirmar si es publica. Preus del XML de 2018–2019: no fiables.</t>
+          <t>Gonçal ha de confirmar si es publica. Preus del XML de 2018–2019: no fiables. | STANDBY (Gonçal, 07/10/2026): no es publica ni es porta a la web nova per ara.</t>
         </is>
       </c>
       <c r="M286" s="2" t="inlineStr">
         <is>
-          <t>Esborrany</t>
+          <t>Standby</t>
         </is>
       </c>
       <c r="N286" s="2" t="inlineStr">
@@ -17362,12 +17366,12 @@
       </c>
       <c r="L288" s="2" t="inlineStr">
         <is>
-          <t>Gonçal ha de confirmar si es publica. Preus del XML de 2018–2019: no fiables.</t>
+          <t>Gonçal ha de confirmar si es publica. Preus del XML de 2018–2019: no fiables. | STANDBY (Gonçal, 07/10/2026): no es publica ni es porta a la web nova per ara.</t>
         </is>
       </c>
       <c r="M288" s="2" t="inlineStr">
         <is>
-          <t>Esborrany</t>
+          <t>Standby</t>
         </is>
       </c>
       <c r="N288" s="2" t="inlineStr">
@@ -17418,12 +17422,12 @@
       </c>
       <c r="L289" s="2" t="inlineStr">
         <is>
-          <t>Gonçal ha de confirmar si es publica. Preus del XML de 2018–2019: no fiables.</t>
+          <t>Gonçal ha de confirmar si es publica. Preus del XML de 2018–2019: no fiables. | STANDBY (Gonçal, 07/10/2026): no es publica ni es porta a la web nova per ara.</t>
         </is>
       </c>
       <c r="M289" s="2" t="inlineStr">
         <is>
-          <t>Esborrany</t>
+          <t>Standby</t>
         </is>
       </c>
       <c r="N289" s="2" t="inlineStr">
@@ -17474,12 +17478,12 @@
       </c>
       <c r="L290" s="2" t="inlineStr">
         <is>
-          <t>Gonçal ha de confirmar si es publica. Preus del XML de 2018–2019: no fiables.</t>
+          <t>Gonçal ha de confirmar si es publica. Preus del XML de 2018–2019: no fiables. | STANDBY (Gonçal, 07/10/2026): no es publica ni es porta a la web nova per ara.</t>
         </is>
       </c>
       <c r="M290" s="2" t="inlineStr">
         <is>
-          <t>Esborrany</t>
+          <t>Standby</t>
         </is>
       </c>
       <c r="N290" s="2" t="inlineStr">
@@ -17530,12 +17534,12 @@
       </c>
       <c r="L291" s="2" t="inlineStr">
         <is>
-          <t>Gonçal ha de confirmar si es publica. Preus del XML de 2018–2019: no fiables.</t>
+          <t>Gonçal ha de confirmar si es publica. Preus del XML de 2018–2019: no fiables. | STANDBY (Gonçal, 07/10/2026): no es publica ni es porta a la web nova per ara.</t>
         </is>
       </c>
       <c r="M291" s="2" t="inlineStr">
         <is>
-          <t>Esborrany</t>
+          <t>Standby</t>
         </is>
       </c>
       <c r="N291" s="2" t="inlineStr">
@@ -17586,12 +17590,12 @@
       </c>
       <c r="L292" s="2" t="inlineStr">
         <is>
-          <t>Gonçal ha de confirmar si es publica. Preus del XML de 2018–2019: no fiables.</t>
+          <t>Gonçal ha de confirmar si es publica. Preus del XML de 2018–2019: no fiables. | STANDBY (Gonçal, 07/10/2026): no es publica ni es porta a la web nova per ara.</t>
         </is>
       </c>
       <c r="M292" s="2" t="inlineStr">
         <is>
-          <t>Esborrany</t>
+          <t>Standby</t>
         </is>
       </c>
       <c r="N292" s="2" t="inlineStr">
@@ -17642,12 +17646,12 @@
       </c>
       <c r="L293" s="2" t="inlineStr">
         <is>
-          <t>Gonçal ha de confirmar si es publica. Preus del XML de 2018–2019: no fiables.</t>
+          <t>Gonçal ha de confirmar si es publica. Preus del XML de 2018–2019: no fiables. | STANDBY (Gonçal, 07/10/2026): no es publica ni es porta a la web nova per ara.</t>
         </is>
       </c>
       <c r="M293" s="2" t="inlineStr">
         <is>
-          <t>Esborrany</t>
+          <t>Standby</t>
         </is>
       </c>
       <c r="N293" s="2" t="inlineStr">
@@ -17698,12 +17702,12 @@
       </c>
       <c r="L294" s="2" t="inlineStr">
         <is>
-          <t>Gonçal ha de confirmar si es publica. Preus del XML de 2018–2019: no fiables.</t>
+          <t>Gonçal ha de confirmar si es publica. Preus del XML de 2018–2019: no fiables. | STANDBY (Gonçal, 07/10/2026): no es publica ni es porta a la web nova per ara.</t>
         </is>
       </c>
       <c r="M294" s="2" t="inlineStr">
         <is>
-          <t>Esborrany</t>
+          <t>Standby</t>
         </is>
       </c>
       <c r="N294" s="2" t="inlineStr">
@@ -17754,12 +17758,12 @@
       </c>
       <c r="L295" s="2" t="inlineStr">
         <is>
-          <t>Gonçal ha de confirmar si es publica. Preus del XML de 2018–2019: no fiables.</t>
+          <t>Gonçal ha de confirmar si es publica. Preus del XML de 2018–2019: no fiables. | STANDBY (Gonçal, 07/10/2026): no es publica ni es porta a la web nova per ara.</t>
         </is>
       </c>
       <c r="M295" s="2" t="inlineStr">
         <is>
-          <t>Esborrany</t>
+          <t>Standby</t>
         </is>
       </c>
       <c r="N295" s="2" t="inlineStr">
@@ -17810,12 +17814,12 @@
       </c>
       <c r="L296" s="2" t="inlineStr">
         <is>
-          <t>Gonçal ha de confirmar si es publica. Preus del XML de 2018–2019: no fiables.</t>
+          <t>Gonçal ha de confirmar si es publica. Preus del XML de 2018–2019: no fiables. | STANDBY (Gonçal, 07/10/2026): no es publica ni es porta a la web nova per ara.</t>
         </is>
       </c>
       <c r="M296" s="2" t="inlineStr">
         <is>
-          <t>Esborrany</t>
+          <t>Standby</t>
         </is>
       </c>
       <c r="N296" s="2" t="inlineStr">
@@ -17866,12 +17870,12 @@
       </c>
       <c r="L297" s="2" t="inlineStr">
         <is>
-          <t>Gonçal ha de confirmar si es publica. Preus del XML de 2018–2019: no fiables.</t>
+          <t>Gonçal ha de confirmar si es publica. Preus del XML de 2018–2019: no fiables. | STANDBY (Gonçal, 07/10/2026): no es publica ni es porta a la web nova per ara.</t>
         </is>
       </c>
       <c r="M297" s="2" t="inlineStr">
         <is>
-          <t>Esborrany</t>
+          <t>Standby</t>
         </is>
       </c>
       <c r="N297" s="2" t="inlineStr">
@@ -17922,12 +17926,12 @@
       </c>
       <c r="L298" s="2" t="inlineStr">
         <is>
-          <t>Gonçal ha de confirmar si es publica. Preus del XML de 2018–2019: no fiables.</t>
+          <t>Gonçal ha de confirmar si es publica. Preus del XML de 2018–2019: no fiables. | STANDBY (Gonçal, 07/10/2026): no es publica ni es porta a la web nova per ara.</t>
         </is>
       </c>
       <c r="M298" s="2" t="inlineStr">
         <is>
-          <t>Esborrany</t>
+          <t>Standby</t>
         </is>
       </c>
       <c r="N298" s="2" t="inlineStr">
@@ -17978,12 +17982,12 @@
       </c>
       <c r="L299" s="2" t="inlineStr">
         <is>
-          <t>Gonçal ha de confirmar si es publica. Preus del XML de 2018–2019: no fiables.</t>
+          <t>Gonçal ha de confirmar si es publica. Preus del XML de 2018–2019: no fiables. | STANDBY (Gonçal, 07/10/2026): no es publica ni es porta a la web nova per ara.</t>
         </is>
       </c>
       <c r="M299" s="2" t="inlineStr">
         <is>
-          <t>Esborrany</t>
+          <t>Standby</t>
         </is>
       </c>
       <c r="N299" s="2" t="inlineStr">
@@ -18034,12 +18038,12 @@
       </c>
       <c r="L300" s="2" t="inlineStr">
         <is>
-          <t>Gonçal ha de confirmar si es publica. Preus del XML de 2018–2019: no fiables.</t>
+          <t>Gonçal ha de confirmar si es publica. Preus del XML de 2018–2019: no fiables. | STANDBY (Gonçal, 07/10/2026): no es publica ni es porta a la web nova per ara.</t>
         </is>
       </c>
       <c r="M300" s="2" t="inlineStr">
         <is>
-          <t>Esborrany</t>
+          <t>Standby</t>
         </is>
       </c>
       <c r="N300" s="2" t="inlineStr">
@@ -18090,12 +18094,12 @@
       </c>
       <c r="L301" s="2" t="inlineStr">
         <is>
-          <t>Gonçal ha de confirmar si es publica. Preus del XML de 2018–2019: no fiables.</t>
+          <t>Gonçal ha de confirmar si es publica. Preus del XML de 2018–2019: no fiables. | STANDBY (Gonçal, 07/10/2026): no es publica ni es porta a la web nova per ara.</t>
         </is>
       </c>
       <c r="M301" s="2" t="inlineStr">
         <is>
-          <t>Esborrany</t>
+          <t>Standby</t>
         </is>
       </c>
       <c r="N301" s="2" t="inlineStr">
@@ -18146,12 +18150,12 @@
       </c>
       <c r="L302" s="2" t="inlineStr">
         <is>
-          <t>Gonçal ha de confirmar si es publica. Preus del XML de 2018–2019: no fiables.</t>
+          <t>Gonçal ha de confirmar si es publica. Preus del XML de 2018–2019: no fiables. | STANDBY (Gonçal, 07/10/2026): no es publica ni es porta a la web nova per ara.</t>
         </is>
       </c>
       <c r="M302" s="2" t="inlineStr">
         <is>
-          <t>Esborrany</t>
+          <t>Standby</t>
         </is>
       </c>
       <c r="N302" s="2" t="inlineStr">
@@ -18202,12 +18206,12 @@
       </c>
       <c r="L303" s="2" t="inlineStr">
         <is>
-          <t>Gonçal ha de confirmar si es publica. Preus del XML de 2018–2019: no fiables.</t>
+          <t>Gonçal ha de confirmar si es publica. Preus del XML de 2018–2019: no fiables. | STANDBY (Gonçal, 07/10/2026): no es publica ni es porta a la web nova per ara.</t>
         </is>
       </c>
       <c r="M303" s="2" t="inlineStr">
         <is>
-          <t>Esborrany</t>
+          <t>Standby</t>
         </is>
       </c>
       <c r="N303" s="2" t="inlineStr">
@@ -18258,12 +18262,12 @@
       </c>
       <c r="L304" s="2" t="inlineStr">
         <is>
-          <t>Gonçal ha de confirmar si es publica. Preus del XML de 2018–2019: no fiables.</t>
+          <t>Gonçal ha de confirmar si es publica. Preus del XML de 2018–2019: no fiables. | STANDBY (Gonçal, 07/10/2026): no es publica ni es porta a la web nova per ara.</t>
         </is>
       </c>
       <c r="M304" s="2" t="inlineStr">
         <is>
-          <t>Esborrany</t>
+          <t>Standby</t>
         </is>
       </c>
       <c r="N304" s="2" t="inlineStr">
@@ -18314,12 +18318,12 @@
       </c>
       <c r="L305" s="2" t="inlineStr">
         <is>
-          <t>Gonçal ha de confirmar si es publica. Preus del XML de 2018–2019: no fiables.</t>
+          <t>Gonçal ha de confirmar si es publica. Preus del XML de 2018–2019: no fiables. | STANDBY (Gonçal, 07/10/2026): no es publica ni es porta a la web nova per ara.</t>
         </is>
       </c>
       <c r="M305" s="2" t="inlineStr">
         <is>
-          <t>Esborrany</t>
+          <t>Standby</t>
         </is>
       </c>
       <c r="N305" s="2" t="inlineStr">
@@ -18370,12 +18374,12 @@
       </c>
       <c r="L306" s="2" t="inlineStr">
         <is>
-          <t>Gonçal ha de confirmar si es publica. Preus del XML de 2018–2019: no fiables.</t>
+          <t>Gonçal ha de confirmar si es publica. Preus del XML de 2018–2019: no fiables. | STANDBY (Gonçal, 07/10/2026): no es publica ni es porta a la web nova per ara.</t>
         </is>
       </c>
       <c r="M306" s="2" t="inlineStr">
         <is>
-          <t>Esborrany</t>
+          <t>Standby</t>
         </is>
       </c>
       <c r="N306" s="2" t="inlineStr">
@@ -18426,12 +18430,12 @@
       </c>
       <c r="L307" s="2" t="inlineStr">
         <is>
-          <t>Gonçal ha de confirmar si es publica. Preus del XML de 2018–2019: no fiables.</t>
+          <t>Gonçal ha de confirmar si es publica. Preus del XML de 2018–2019: no fiables. | STANDBY (Gonçal, 07/10/2026): no es publica ni es porta a la web nova per ara.</t>
         </is>
       </c>
       <c r="M307" s="2" t="inlineStr">
         <is>
-          <t>Esborrany</t>
+          <t>Standby</t>
         </is>
       </c>
       <c r="N307" s="2" t="inlineStr">
@@ -18534,12 +18538,12 @@
       </c>
       <c r="L309" s="2" t="inlineStr">
         <is>
-          <t>Gonçal ha de confirmar si es publica. Preus del XML de 2018–2019: no fiables.</t>
+          <t>Gonçal ha de confirmar si es publica. Preus del XML de 2018–2019: no fiables. | STANDBY (Gonçal, 07/10/2026): no es publica ni es porta a la web nova per ara.</t>
         </is>
       </c>
       <c r="M309" s="2" t="inlineStr">
         <is>
-          <t>Esborrany</t>
+          <t>Standby</t>
         </is>
       </c>
       <c r="N309" s="2" t="inlineStr">
@@ -18592,12 +18596,12 @@
       </c>
       <c r="L310" s="2" t="inlineStr">
         <is>
-          <t>Idioma deduït del títol. Gonçal ha de confirmar si es publica.</t>
+          <t>Idioma deduït del títol. Gonçal ha de confirmar si es publica. | STANDBY (Gonçal, 07/10/2026): no es publica ni es porta a la web nova per ara.</t>
         </is>
       </c>
       <c r="M310" s="2" t="inlineStr">
         <is>
-          <t>Esborrany</t>
+          <t>Standby</t>
         </is>
       </c>
       <c r="N310" s="2" t="inlineStr">
@@ -18650,12 +18654,12 @@
       </c>
       <c r="L311" s="2" t="inlineStr">
         <is>
-          <t>Idioma deduït del títol. Gonçal ha de confirmar si es publica.</t>
+          <t>Idioma deduït del títol. Gonçal ha de confirmar si es publica. | STANDBY (Gonçal, 07/10/2026): no es publica ni es porta a la web nova per ara.</t>
         </is>
       </c>
       <c r="M311" s="2" t="inlineStr">
         <is>
-          <t>Esborrany</t>
+          <t>Standby</t>
         </is>
       </c>
       <c r="N311" s="2" t="inlineStr">
@@ -18708,12 +18712,12 @@
       </c>
       <c r="L312" s="2" t="inlineStr">
         <is>
-          <t>Idioma deduït del títol. Gonçal ha de confirmar si es publica.</t>
+          <t>Idioma deduït del títol. Gonçal ha de confirmar si es publica. | STANDBY (Gonçal, 07/10/2026): no es publica ni es porta a la web nova per ara.</t>
         </is>
       </c>
       <c r="M312" s="2" t="inlineStr">
         <is>
-          <t>Esborrany</t>
+          <t>Standby</t>
         </is>
       </c>
       <c r="N312" s="2" t="inlineStr">
@@ -18766,12 +18770,12 @@
       </c>
       <c r="L313" s="2" t="inlineStr">
         <is>
-          <t>Idioma deduït del títol. Gonçal ha de confirmar si es publica.</t>
+          <t>Idioma deduït del títol. Gonçal ha de confirmar si es publica. | STANDBY (Gonçal, 07/10/2026): no es publica ni es porta a la web nova per ara.</t>
         </is>
       </c>
       <c r="M313" s="2" t="inlineStr">
         <is>
-          <t>Esborrany</t>
+          <t>Standby</t>
         </is>
       </c>
       <c r="N313" s="2" t="inlineStr">
@@ -18824,12 +18828,12 @@
       </c>
       <c r="L314" s="2" t="inlineStr">
         <is>
-          <t>Idioma deduït del títol. Gonçal ha de confirmar si es publica.</t>
+          <t>Idioma deduït del títol. Gonçal ha de confirmar si es publica. | STANDBY (Gonçal, 07/10/2026): no es publica ni es porta a la web nova per ara.</t>
         </is>
       </c>
       <c r="M314" s="2" t="inlineStr">
         <is>
-          <t>Esborrany</t>
+          <t>Standby</t>
         </is>
       </c>
       <c r="N314" s="2" t="inlineStr">
@@ -18882,12 +18886,12 @@
       </c>
       <c r="L315" s="2" t="inlineStr">
         <is>
-          <t>Idioma deduït del títol. Gonçal ha de confirmar si es publica.</t>
+          <t>Idioma deduït del títol. Gonçal ha de confirmar si es publica. | STANDBY (Gonçal, 07/10/2026): no es publica ni es porta a la web nova per ara.</t>
         </is>
       </c>
       <c r="M315" s="2" t="inlineStr">
         <is>
-          <t>Esborrany</t>
+          <t>Standby</t>
         </is>
       </c>
       <c r="N315" s="2" t="inlineStr">
@@ -18940,12 +18944,12 @@
       </c>
       <c r="L316" s="2" t="inlineStr">
         <is>
-          <t>Idioma deduït del títol. Gonçal ha de confirmar si es publica.</t>
+          <t>Idioma deduït del títol. Gonçal ha de confirmar si es publica. | STANDBY (Gonçal, 07/10/2026): no es publica ni es porta a la web nova per ara.</t>
         </is>
       </c>
       <c r="M316" s="2" t="inlineStr">
         <is>
-          <t>Esborrany</t>
+          <t>Standby</t>
         </is>
       </c>
       <c r="N316" s="2" t="inlineStr">
@@ -18998,12 +19002,12 @@
       </c>
       <c r="L317" s="2" t="inlineStr">
         <is>
-          <t>Idioma deduït del títol. Gonçal ha de confirmar si es publica.</t>
+          <t>Idioma deduït del títol. Gonçal ha de confirmar si es publica. | STANDBY (Gonçal, 07/10/2026): no es publica ni es porta a la web nova per ara.</t>
         </is>
       </c>
       <c r="M317" s="2" t="inlineStr">
         <is>
-          <t>Esborrany</t>
+          <t>Standby</t>
         </is>
       </c>
       <c r="N317" s="2" t="inlineStr">
@@ -19056,12 +19060,12 @@
       </c>
       <c r="L318" s="2" t="inlineStr">
         <is>
-          <t>Idioma deduït del títol. Gonçal ha de confirmar si es publica.</t>
+          <t>Idioma deduït del títol. Gonçal ha de confirmar si es publica. | STANDBY (Gonçal, 07/10/2026): no es publica ni es porta a la web nova per ara.</t>
         </is>
       </c>
       <c r="M318" s="2" t="inlineStr">
         <is>
-          <t>Esborrany</t>
+          <t>Standby</t>
         </is>
       </c>
       <c r="N318" s="2" t="inlineStr">
@@ -19114,12 +19118,12 @@
       </c>
       <c r="L319" s="2" t="inlineStr">
         <is>
-          <t>Idioma deduït del títol. Gonçal ha de confirmar si es publica.</t>
+          <t>Idioma deduït del títol. Gonçal ha de confirmar si es publica. | STANDBY (Gonçal, 07/10/2026): no es publica ni es porta a la web nova per ara.</t>
         </is>
       </c>
       <c r="M319" s="2" t="inlineStr">
         <is>
-          <t>Esborrany</t>
+          <t>Standby</t>
         </is>
       </c>
       <c r="N319" s="2" t="inlineStr">
@@ -19172,12 +19176,12 @@
       </c>
       <c r="L320" s="2" t="inlineStr">
         <is>
-          <t>Idioma deduït del títol. Gonçal ha de confirmar si es publica.</t>
+          <t>Idioma deduït del títol. Gonçal ha de confirmar si es publica. | STANDBY (Gonçal, 07/10/2026): no es publica ni es porta a la web nova per ara.</t>
         </is>
       </c>
       <c r="M320" s="2" t="inlineStr">
         <is>
-          <t>Esborrany</t>
+          <t>Standby</t>
         </is>
       </c>
       <c r="N320" s="2" t="inlineStr">
@@ -19230,12 +19234,12 @@
       </c>
       <c r="L321" s="2" t="inlineStr">
         <is>
-          <t>Idioma deduït del títol. Gonçal ha de confirmar si es publica.</t>
+          <t>Idioma deduït del títol. Gonçal ha de confirmar si es publica. | STANDBY (Gonçal, 07/10/2026): no es publica ni es porta a la web nova per ara.</t>
         </is>
       </c>
       <c r="M321" s="2" t="inlineStr">
         <is>
-          <t>Esborrany</t>
+          <t>Standby</t>
         </is>
       </c>
       <c r="N321" s="2" t="inlineStr">
@@ -19288,12 +19292,12 @@
       </c>
       <c r="L322" s="2" t="inlineStr">
         <is>
-          <t>Idioma deduït del títol. Gonçal ha de confirmar si es publica.</t>
+          <t>Idioma deduït del títol. Gonçal ha de confirmar si es publica. | STANDBY (Gonçal, 07/10/2026): no es publica ni es porta a la web nova per ara.</t>
         </is>
       </c>
       <c r="M322" s="2" t="inlineStr">
         <is>
-          <t>Esborrany</t>
+          <t>Standby</t>
         </is>
       </c>
       <c r="N322" s="2" t="inlineStr">
@@ -19346,12 +19350,12 @@
       </c>
       <c r="L323" s="2" t="inlineStr">
         <is>
-          <t>Idioma deduït del títol. Gonçal ha de confirmar si es publica.</t>
+          <t>Idioma deduït del títol. Gonçal ha de confirmar si es publica. | STANDBY (Gonçal, 07/10/2026): no es publica ni es porta a la web nova per ara.</t>
         </is>
       </c>
       <c r="M323" s="2" t="inlineStr">
         <is>
-          <t>Esborrany</t>
+          <t>Standby</t>
         </is>
       </c>
       <c r="N323" s="2" t="inlineStr">
@@ -19404,12 +19408,12 @@
       </c>
       <c r="L324" s="2" t="inlineStr">
         <is>
-          <t>Idioma deduït del títol. Gonçal ha de confirmar si es publica.</t>
+          <t>Idioma deduït del títol. Gonçal ha de confirmar si es publica. | STANDBY (Gonçal, 07/10/2026): no es publica ni es porta a la web nova per ara.</t>
         </is>
       </c>
       <c r="M324" s="2" t="inlineStr">
         <is>
-          <t>Esborrany</t>
+          <t>Standby</t>
         </is>
       </c>
       <c r="N324" s="2" t="inlineStr">
@@ -19462,12 +19466,12 @@
       </c>
       <c r="L325" s="2" t="inlineStr">
         <is>
-          <t>Idioma deduït del títol. Gonçal ha de confirmar si es publica.</t>
+          <t>Idioma deduït del títol. Gonçal ha de confirmar si es publica. | STANDBY (Gonçal, 07/10/2026): no es publica ni es porta a la web nova per ara.</t>
         </is>
       </c>
       <c r="M325" s="2" t="inlineStr">
         <is>
-          <t>Esborrany</t>
+          <t>Standby</t>
         </is>
       </c>
       <c r="N325" s="2" t="inlineStr">
@@ -19520,12 +19524,12 @@
       </c>
       <c r="L326" s="2" t="inlineStr">
         <is>
-          <t>Idioma deduït del títol. Gonçal ha de confirmar si es publica.</t>
+          <t>Idioma deduït del títol. Gonçal ha de confirmar si es publica. | STANDBY (Gonçal, 07/10/2026): no es publica ni es porta a la web nova per ara.</t>
         </is>
       </c>
       <c r="M326" s="2" t="inlineStr">
         <is>
-          <t>Esborrany</t>
+          <t>Standby</t>
         </is>
       </c>
       <c r="N326" s="2" t="inlineStr">
@@ -19578,12 +19582,12 @@
       </c>
       <c r="L327" s="2" t="inlineStr">
         <is>
-          <t>Idioma deduït del títol. Gonçal ha de confirmar si es publica.</t>
+          <t>Idioma deduït del títol. Gonçal ha de confirmar si es publica. | STANDBY (Gonçal, 07/10/2026): no es publica ni es porta a la web nova per ara.</t>
         </is>
       </c>
       <c r="M327" s="2" t="inlineStr">
         <is>
-          <t>Esborrany</t>
+          <t>Standby</t>
         </is>
       </c>
       <c r="N327" s="2" t="inlineStr">
@@ -19624,27 +19628,27 @@
           <t>Contingut de blog (consells i actualitat de viatge)</t>
         </is>
       </c>
-      <c r="J328" s="10" t="inlineStr">
-        <is>
-          <t>Pendent</t>
+      <c r="J328" s="5" t="inlineStr">
+        <is>
+          <t>Eliminar</t>
         </is>
       </c>
       <c r="K328" s="2" t="inlineStr">
         <is>
-          <t>A la paperera. Gonçal ha dit «tot», però la majoria són versions antigues o duplicades d'entrades ja publicades: proposem NO migrar-la.</t>
-        </is>
-      </c>
-      <c r="L328" s="2" t="inlineStr">
-        <is>
-          <t>Gonçal ha de confirmar.</t>
-        </is>
-      </c>
+          <t>A la paperera. Gonçal confirma (07/10/2026) que es deixen fora.</t>
+        </is>
+      </c>
+      <c r="L328" s="2" t="inlineStr"/>
       <c r="M328" s="2" t="inlineStr">
         <is>
           <t>Paperera</t>
         </is>
       </c>
-      <c r="N328" s="2" t="inlineStr"/>
+      <c r="N328" s="2" t="inlineStr">
+        <is>
+          <t>(no es migra)</t>
+        </is>
+      </c>
     </row>
     <row r="329">
       <c r="A329" s="2" t="inlineStr">
@@ -19678,27 +19682,27 @@
           <t>Contingut de blog (consells i actualitat de viatge)</t>
         </is>
       </c>
-      <c r="J329" s="10" t="inlineStr">
-        <is>
-          <t>Pendent</t>
+      <c r="J329" s="5" t="inlineStr">
+        <is>
+          <t>Eliminar</t>
         </is>
       </c>
       <c r="K329" s="2" t="inlineStr">
         <is>
-          <t>A la paperera. Gonçal ha dit «tot», però la majoria són versions antigues o duplicades d'entrades ja publicades: proposem NO migrar-la.</t>
-        </is>
-      </c>
-      <c r="L329" s="2" t="inlineStr">
-        <is>
-          <t>Gonçal ha de confirmar.</t>
-        </is>
-      </c>
+          <t>A la paperera. Gonçal confirma (07/10/2026) que es deixen fora.</t>
+        </is>
+      </c>
+      <c r="L329" s="2" t="inlineStr"/>
       <c r="M329" s="2" t="inlineStr">
         <is>
           <t>Paperera</t>
         </is>
       </c>
-      <c r="N329" s="2" t="inlineStr"/>
+      <c r="N329" s="2" t="inlineStr">
+        <is>
+          <t>(no es migra)</t>
+        </is>
+      </c>
     </row>
     <row r="330">
       <c r="A330" s="2" t="inlineStr">
@@ -19732,27 +19736,27 @@
           <t>Contingut de blog (consells i actualitat de viatge)</t>
         </is>
       </c>
-      <c r="J330" s="10" t="inlineStr">
-        <is>
-          <t>Pendent</t>
+      <c r="J330" s="5" t="inlineStr">
+        <is>
+          <t>Eliminar</t>
         </is>
       </c>
       <c r="K330" s="2" t="inlineStr">
         <is>
-          <t>A la paperera. Gonçal ha dit «tot», però la majoria són versions antigues o duplicades d'entrades ja publicades: proposem NO migrar-la.</t>
-        </is>
-      </c>
-      <c r="L330" s="2" t="inlineStr">
-        <is>
-          <t>Gonçal ha de confirmar.</t>
-        </is>
-      </c>
+          <t>A la paperera. Gonçal confirma (07/10/2026) que es deixen fora.</t>
+        </is>
+      </c>
+      <c r="L330" s="2" t="inlineStr"/>
       <c r="M330" s="2" t="inlineStr">
         <is>
           <t>Paperera</t>
         </is>
       </c>
-      <c r="N330" s="2" t="inlineStr"/>
+      <c r="N330" s="2" t="inlineStr">
+        <is>
+          <t>(no es migra)</t>
+        </is>
+      </c>
     </row>
     <row r="331">
       <c r="A331" s="2" t="inlineStr">
@@ -19786,27 +19790,27 @@
           <t>Contingut de blog (consells i actualitat de viatge)</t>
         </is>
       </c>
-      <c r="J331" s="10" t="inlineStr">
-        <is>
-          <t>Pendent</t>
+      <c r="J331" s="5" t="inlineStr">
+        <is>
+          <t>Eliminar</t>
         </is>
       </c>
       <c r="K331" s="2" t="inlineStr">
         <is>
-          <t>A la paperera. Gonçal ha dit «tot», però la majoria són versions antigues o duplicades d'entrades ja publicades: proposem NO migrar-la.</t>
-        </is>
-      </c>
-      <c r="L331" s="2" t="inlineStr">
-        <is>
-          <t>Gonçal ha de confirmar.</t>
-        </is>
-      </c>
+          <t>A la paperera. Gonçal confirma (07/10/2026) que es deixen fora.</t>
+        </is>
+      </c>
+      <c r="L331" s="2" t="inlineStr"/>
       <c r="M331" s="2" t="inlineStr">
         <is>
           <t>Paperera</t>
         </is>
       </c>
-      <c r="N331" s="2" t="inlineStr"/>
+      <c r="N331" s="2" t="inlineStr">
+        <is>
+          <t>(no es migra)</t>
+        </is>
+      </c>
     </row>
     <row r="332">
       <c r="A332" s="2" t="inlineStr">
@@ -19840,27 +19844,27 @@
           <t>Contingut de blog (consells i actualitat de viatge)</t>
         </is>
       </c>
-      <c r="J332" s="10" t="inlineStr">
-        <is>
-          <t>Pendent</t>
+      <c r="J332" s="5" t="inlineStr">
+        <is>
+          <t>Eliminar</t>
         </is>
       </c>
       <c r="K332" s="2" t="inlineStr">
         <is>
-          <t>A la paperera. Gonçal ha dit «tot», però la majoria són versions antigues o duplicades d'entrades ja publicades: proposem NO migrar-la.</t>
-        </is>
-      </c>
-      <c r="L332" s="2" t="inlineStr">
-        <is>
-          <t>Gonçal ha de confirmar.</t>
-        </is>
-      </c>
+          <t>A la paperera. Gonçal confirma (07/10/2026) que es deixen fora.</t>
+        </is>
+      </c>
+      <c r="L332" s="2" t="inlineStr"/>
       <c r="M332" s="2" t="inlineStr">
         <is>
           <t>Paperera</t>
         </is>
       </c>
-      <c r="N332" s="2" t="inlineStr"/>
+      <c r="N332" s="2" t="inlineStr">
+        <is>
+          <t>(no es migra)</t>
+        </is>
+      </c>
     </row>
     <row r="333">
       <c r="A333" s="2" t="inlineStr">
@@ -19894,27 +19898,27 @@
           <t>Contingut de blog (consells i actualitat de viatge)</t>
         </is>
       </c>
-      <c r="J333" s="10" t="inlineStr">
-        <is>
-          <t>Pendent</t>
+      <c r="J333" s="5" t="inlineStr">
+        <is>
+          <t>Eliminar</t>
         </is>
       </c>
       <c r="K333" s="2" t="inlineStr">
         <is>
-          <t>A la paperera. Gonçal ha dit «tot», però la majoria són versions antigues o duplicades d'entrades ja publicades: proposem NO migrar-la.</t>
-        </is>
-      </c>
-      <c r="L333" s="2" t="inlineStr">
-        <is>
-          <t>Gonçal ha de confirmar.</t>
-        </is>
-      </c>
+          <t>A la paperera. Gonçal confirma (07/10/2026) que es deixen fora.</t>
+        </is>
+      </c>
+      <c r="L333" s="2" t="inlineStr"/>
       <c r="M333" s="2" t="inlineStr">
         <is>
           <t>Paperera</t>
         </is>
       </c>
-      <c r="N333" s="2" t="inlineStr"/>
+      <c r="N333" s="2" t="inlineStr">
+        <is>
+          <t>(no es migra)</t>
+        </is>
+      </c>
     </row>
     <row r="334">
       <c r="A334" s="2" t="inlineStr">
@@ -19948,27 +19952,27 @@
           <t>Contingut de blog (consells i actualitat de viatge)</t>
         </is>
       </c>
-      <c r="J334" s="10" t="inlineStr">
-        <is>
-          <t>Pendent</t>
+      <c r="J334" s="5" t="inlineStr">
+        <is>
+          <t>Eliminar</t>
         </is>
       </c>
       <c r="K334" s="2" t="inlineStr">
         <is>
-          <t>A la paperera. Gonçal ha dit «tot», però la majoria són versions antigues o duplicades d'entrades ja publicades: proposem NO migrar-la.</t>
-        </is>
-      </c>
-      <c r="L334" s="2" t="inlineStr">
-        <is>
-          <t>Gonçal ha de confirmar.</t>
-        </is>
-      </c>
+          <t>A la paperera. Gonçal confirma (07/10/2026) que es deixen fora.</t>
+        </is>
+      </c>
+      <c r="L334" s="2" t="inlineStr"/>
       <c r="M334" s="2" t="inlineStr">
         <is>
           <t>Paperera</t>
         </is>
       </c>
-      <c r="N334" s="2" t="inlineStr"/>
+      <c r="N334" s="2" t="inlineStr">
+        <is>
+          <t>(no es migra)</t>
+        </is>
+      </c>
     </row>
     <row r="335">
       <c r="A335" s="2" t="inlineStr">
@@ -20002,27 +20006,27 @@
           <t>Contingut de blog (consells i actualitat de viatge)</t>
         </is>
       </c>
-      <c r="J335" s="10" t="inlineStr">
-        <is>
-          <t>Pendent</t>
+      <c r="J335" s="5" t="inlineStr">
+        <is>
+          <t>Eliminar</t>
         </is>
       </c>
       <c r="K335" s="2" t="inlineStr">
         <is>
-          <t>A la paperera. Gonçal ha dit «tot», però la majoria són versions antigues o duplicades d'entrades ja publicades: proposem NO migrar-la.</t>
-        </is>
-      </c>
-      <c r="L335" s="2" t="inlineStr">
-        <is>
-          <t>Gonçal ha de confirmar.</t>
-        </is>
-      </c>
+          <t>A la paperera. Gonçal confirma (07/10/2026) que es deixen fora.</t>
+        </is>
+      </c>
+      <c r="L335" s="2" t="inlineStr"/>
       <c r="M335" s="2" t="inlineStr">
         <is>
           <t>Paperera</t>
         </is>
       </c>
-      <c r="N335" s="2" t="inlineStr"/>
+      <c r="N335" s="2" t="inlineStr">
+        <is>
+          <t>(no es migra)</t>
+        </is>
+      </c>
     </row>
     <row r="336">
       <c r="A336" s="2" t="inlineStr">
@@ -20056,27 +20060,27 @@
           <t>Contingut de blog (consells i actualitat de viatge)</t>
         </is>
       </c>
-      <c r="J336" s="10" t="inlineStr">
-        <is>
-          <t>Pendent</t>
+      <c r="J336" s="5" t="inlineStr">
+        <is>
+          <t>Eliminar</t>
         </is>
       </c>
       <c r="K336" s="2" t="inlineStr">
         <is>
-          <t>A la paperera. Gonçal ha dit «tot», però la majoria són versions antigues o duplicades d'entrades ja publicades: proposem NO migrar-la.</t>
-        </is>
-      </c>
-      <c r="L336" s="2" t="inlineStr">
-        <is>
-          <t>Gonçal ha de confirmar.</t>
-        </is>
-      </c>
+          <t>A la paperera. Gonçal confirma (07/10/2026) que es deixen fora.</t>
+        </is>
+      </c>
+      <c r="L336" s="2" t="inlineStr"/>
       <c r="M336" s="2" t="inlineStr">
         <is>
           <t>Paperera</t>
         </is>
       </c>
-      <c r="N336" s="2" t="inlineStr"/>
+      <c r="N336" s="2" t="inlineStr">
+        <is>
+          <t>(no es migra)</t>
+        </is>
+      </c>
     </row>
     <row r="337">
       <c r="A337" s="2" t="inlineStr">
@@ -20110,27 +20114,27 @@
           <t>Contingut de blog (consells i actualitat de viatge)</t>
         </is>
       </c>
-      <c r="J337" s="10" t="inlineStr">
-        <is>
-          <t>Pendent</t>
+      <c r="J337" s="5" t="inlineStr">
+        <is>
+          <t>Eliminar</t>
         </is>
       </c>
       <c r="K337" s="2" t="inlineStr">
         <is>
-          <t>A la paperera. Gonçal ha dit «tot», però la majoria són versions antigues o duplicades d'entrades ja publicades: proposem NO migrar-la.</t>
-        </is>
-      </c>
-      <c r="L337" s="2" t="inlineStr">
-        <is>
-          <t>Gonçal ha de confirmar.</t>
-        </is>
-      </c>
+          <t>A la paperera. Gonçal confirma (07/10/2026) que es deixen fora.</t>
+        </is>
+      </c>
+      <c r="L337" s="2" t="inlineStr"/>
       <c r="M337" s="2" t="inlineStr">
         <is>
           <t>Paperera</t>
         </is>
       </c>
-      <c r="N337" s="2" t="inlineStr"/>
+      <c r="N337" s="2" t="inlineStr">
+        <is>
+          <t>(no es migra)</t>
+        </is>
+      </c>
     </row>
     <row r="338">
       <c r="A338" s="2" t="inlineStr">
@@ -20214,19 +20218,19 @@
           <t>Pagina informativa o comercial del web</t>
         </is>
       </c>
-      <c r="J339" s="4" t="inlineStr">
-        <is>
-          <t>Mantener</t>
+      <c r="J339" s="3" t="inlineStr">
+        <is>
+          <t>Fusionar</t>
         </is>
       </c>
       <c r="K339" s="2" t="inlineStr">
         <is>
-          <t>Sisena línia de negoci (Gonçal, 07/10/2026). Esborrany del 24/09/2026 amb contingut real.</t>
+          <t>Gonçal (07/10/2026): Valua Services és la mateixa pàgina que /serveis/. Es fusiona amb ella.</t>
         </is>
       </c>
       <c r="L339" s="2" t="inlineStr">
         <is>
-          <t>[PENDENT] slug i relació amb /serveis/.</t>
+          <t>[PENDENT] quina redacció preval: la de /serveis/ o aquest esborrany.</t>
         </is>
       </c>
       <c r="M339" s="2" t="inlineStr">
@@ -20236,7 +20240,7 @@
       </c>
       <c r="N339" s="2" t="inlineStr">
         <is>
-          <t>[PENDENT]</t>
+          <t>/serveis/</t>
         </is>
       </c>
     </row>
@@ -20550,12 +20554,12 @@
       </c>
       <c r="L345" s="2" t="inlineStr">
         <is>
-          <t>[PENDENT] text de Gonçal.</t>
+          <t>STANDBY (Gonçal, 07/10/2026): sense text; no es dissenya ara.</t>
         </is>
       </c>
       <c r="M345" s="2" t="inlineStr">
         <is>
-          <t>Nova</t>
+          <t>Standby</t>
         </is>
       </c>
       <c r="N345" s="2" t="inlineStr">
@@ -20606,12 +20610,12 @@
       </c>
       <c r="L346" s="2" t="inlineStr">
         <is>
-          <t>[PENDENT] text de Gonçal.</t>
+          <t>STANDBY (Gonçal, 07/10/2026): sense text; no es dissenya ara.</t>
         </is>
       </c>
       <c r="M346" s="2" t="inlineStr">
         <is>
-          <t>Nova</t>
+          <t>Standby</t>
         </is>
       </c>
       <c r="N346" s="2" t="inlineStr">
@@ -20955,13 +20959,13 @@
         <v>0</v>
       </c>
       <c r="E11" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="F11" t="n">
         <v>0</v>
       </c>
       <c r="G11" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="H11" t="n">
         <v>10</v>
@@ -21198,13 +21202,13 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C20" t="n">
         <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E20" t="n">
         <v>1</v>
@@ -21338,22 +21342,22 @@
         </is>
       </c>
       <c r="B25" s="8" t="n">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="C25" s="8" t="n">
         <v>7</v>
       </c>
       <c r="D25" s="8" t="n">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="E25" s="8" t="n">
-        <v>33</v>
+        <v>43</v>
       </c>
       <c r="F25" s="8" t="n">
         <v>2</v>
       </c>
       <c r="G25" s="8" t="n">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="H25" s="8" t="n">
         <v>345</v>
@@ -21383,6 +21387,7 @@
         </is>
       </c>
     </row>
+    <row r="2"/>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
@@ -21411,6 +21416,7 @@
         </is>
       </c>
     </row>
+    <row r="7"/>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
@@ -21428,7 +21434,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Decisions de Goncal (07/10/2026) aplicades: web informativa; tours amb una fitxa per desti i selector de durada (les versions per durada passen a 'Fusionar'); Valua Groups i I2EU amb pagina propia ('Crear'); Tribes i Services com a linies; es migra tot; idiomes CA/ES/EN.</t>
+          <t>Decisions de Goncal (07/10/2026) aplicades: web informativa; tours amb una fitxa per desti i selector de durada (les versions per durada passen a 'Fusionar'); Valua Groups i I2EU amb pagina propia ('Crear'); Tribes i Services com a linies; es migra tot; idiomes CA/ES/EN. Segona tanda (07/10): Valua Services = /serveis/; Groups i I2EU, esborranys (24 tours, 18 entrades) i peu de pagina en STANDBY (columna Estat); entrades de paperera = Eliminar; Area Client externa, no es crea.</t>
         </is>
       </c>
     </row>
@@ -21740,13 +21746,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{EC955712-7263-40E6-B60A-A32B4BB91C91}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4C0B5169-CECF-4857-AF34-4BE5F53293A6}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0C45F693-AFEA-4D13-A566-1AE2B6A92162}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6C751B4A-5A81-4A74-8EC7-6CAB4DD8C8AE}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5333A482-BD49-4DCA-A1D0-6C04322CD02F}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{865A3798-CBEE-4048-9AF2-E75B12C6E485}"/>
 </file>